--- a/static/data/exports/Retro_BR_AE-BP_2019.xlsx
+++ b/static/data/exports/Retro_BR_AE-BP_2019.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,6 +576,9 @@
           <t>AIMIM</t>
         </is>
       </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
       <c r="R2" t="n">
         <v>36</v>
       </c>
@@ -635,6 +638,9 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
       <c r="R3" t="n">
         <v>36</v>
       </c>
@@ -694,6 +700,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
       <c r="R4" t="n">
         <v>36</v>
       </c>
@@ -753,6 +762,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
       <c r="R5" t="n">
         <v>36</v>
       </c>
@@ -812,6 +824,9 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
       <c r="R6" t="n">
         <v>36</v>
       </c>
@@ -871,6 +886,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
       <c r="R7" t="n">
         <v>36</v>
       </c>
@@ -930,6 +948,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
       <c r="R8" t="n">
         <v>36</v>
       </c>
@@ -989,6 +1010,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
       <c r="R9" t="n">
         <v>36</v>
       </c>
@@ -1048,6 +1072,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
       <c r="R10" t="n">
         <v>36</v>
       </c>
@@ -1107,6 +1134,9 @@
           <t>RJD</t>
         </is>
       </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
       <c r="R11" t="n">
         <v>36</v>
       </c>
@@ -1166,6 +1196,9 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
       <c r="R12" t="n">
         <v>36</v>
       </c>
@@ -1225,6 +1258,9 @@
           <t>VSIP</t>
         </is>
       </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
       <c r="R13" t="n">
         <v>36</v>
       </c>
@@ -1284,6 +1320,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
       <c r="R14" t="n">
         <v>36</v>
       </c>
@@ -1343,6 +1382,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
       <c r="R15" t="n">
         <v>36</v>
       </c>
@@ -1402,6 +1444,9 @@
           <t>AKBMP</t>
         </is>
       </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
       <c r="R16" t="n">
         <v>36</v>
       </c>
@@ -1461,6 +1506,9 @@
           <t>RJBP</t>
         </is>
       </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
       <c r="R17" t="n">
         <v>36</v>
       </c>
@@ -1520,6 +1568,9 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
       <c r="R18" t="n">
         <v>36</v>
       </c>
@@ -1579,6 +1630,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
       <c r="R19" t="n">
         <v>36</v>
       </c>
@@ -1638,6 +1692,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
       <c r="R20" t="n">
         <v>36</v>
       </c>
@@ -1697,6 +1754,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
       <c r="R21" t="n">
         <v>36</v>
       </c>
@@ -1756,6 +1816,9 @@
           <t>JANADIP</t>
         </is>
       </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
       <c r="R22" t="n">
         <v>36</v>
       </c>
@@ -1815,6 +1878,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
       <c r="R23" t="n">
         <v>36</v>
       </c>
@@ -1874,6 +1940,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
       <c r="R24" t="n">
         <v>36</v>
       </c>
@@ -1933,6 +2002,9 @@
           <t>YKP</t>
         </is>
       </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
       <c r="R25" t="n">
         <v>36</v>
       </c>
@@ -1992,6 +2064,9 @@
           <t>WAP</t>
         </is>
       </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
       <c r="R26" t="n">
         <v>36</v>
       </c>
@@ -2051,6 +2126,9 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
       <c r="R27" t="n">
         <v>36</v>
       </c>
@@ -2110,6 +2188,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
       <c r="R28" t="n">
         <v>36</v>
       </c>
@@ -2169,6 +2250,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
       <c r="R29" t="n">
         <v>36</v>
       </c>
@@ -2228,6 +2312,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
       <c r="R30" t="n">
         <v>36</v>
       </c>
@@ -2287,6 +2374,9 @@
           <t>JANADIP</t>
         </is>
       </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
       <c r="R31" t="n">
         <v>36</v>
       </c>
@@ -2346,6 +2436,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
       <c r="R32" t="n">
         <v>36</v>
       </c>
@@ -2405,6 +2498,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q33" t="b">
+        <v>0</v>
+      </c>
       <c r="R33" t="n">
         <v>36</v>
       </c>
@@ -2464,6 +2560,9 @@
           <t>YKP</t>
         </is>
       </c>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
       <c r="R34" t="n">
         <v>36</v>
       </c>
@@ -2523,6 +2622,9 @@
           <t>WAP</t>
         </is>
       </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
       <c r="R35" t="n">
         <v>36</v>
       </c>
@@ -2582,6 +2684,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
       <c r="R36" t="n">
         <v>36</v>
       </c>
@@ -2641,6 +2746,9 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
       <c r="R37" t="n">
         <v>36</v>
       </c>
@@ -2700,6 +2808,9 @@
           <t>RJD</t>
         </is>
       </c>
+      <c r="Q38" t="b">
+        <v>0</v>
+      </c>
       <c r="R38" t="n">
         <v>36</v>
       </c>
@@ -2759,6 +2870,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
       <c r="R39" t="n">
         <v>36</v>
       </c>
@@ -2818,6 +2932,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
       <c r="R40" t="n">
         <v>36</v>
       </c>
@@ -2877,6 +2994,9 @@
           <t>CP(ML) (L)</t>
         </is>
       </c>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
       <c r="R41" t="n">
         <v>36</v>
       </c>
@@ -2936,6 +3056,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
       <c r="R42" t="n">
         <v>36</v>
       </c>
@@ -2995,6 +3118,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
       <c r="R43" t="n">
         <v>36</v>
       </c>
@@ -3054,6 +3180,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
       <c r="R44" t="n">
         <v>36</v>
       </c>
@@ -3113,6 +3242,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
       <c r="R45" t="n">
         <v>36</v>
       </c>
@@ -3172,6 +3304,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q46" t="b">
+        <v>0</v>
+      </c>
       <c r="R46" t="n">
         <v>36</v>
       </c>
@@ -3231,6 +3366,9 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
       <c r="R47" t="n">
         <v>36</v>
       </c>
@@ -3290,6 +3428,9 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="Q48" t="b">
+        <v>0</v>
+      </c>
       <c r="R48" t="n">
         <v>36</v>
       </c>
@@ -3349,6 +3490,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q49" t="b">
+        <v>0</v>
+      </c>
       <c r="R49" t="n">
         <v>36</v>
       </c>
@@ -3408,6 +3552,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q50" t="b">
+        <v>0</v>
+      </c>
       <c r="R50" t="n">
         <v>36</v>
       </c>
@@ -3467,6 +3614,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q51" t="b">
+        <v>0</v>
+      </c>
       <c r="R51" t="n">
         <v>36</v>
       </c>
@@ -3526,6 +3676,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q52" t="b">
+        <v>0</v>
+      </c>
       <c r="R52" t="n">
         <v>36</v>
       </c>
@@ -3585,6 +3738,9 @@
           <t>JANADIP</t>
         </is>
       </c>
+      <c r="Q53" t="b">
+        <v>0</v>
+      </c>
       <c r="R53" t="n">
         <v>36</v>
       </c>
@@ -3644,6 +3800,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q54" t="b">
+        <v>0</v>
+      </c>
       <c r="R54" t="n">
         <v>36</v>
       </c>
@@ -3703,6 +3862,9 @@
           <t>YKP</t>
         </is>
       </c>
+      <c r="Q55" t="b">
+        <v>0</v>
+      </c>
       <c r="R55" t="n">
         <v>36</v>
       </c>
@@ -3762,6 +3924,9 @@
           <t>WAP</t>
         </is>
       </c>
+      <c r="Q56" t="b">
+        <v>0</v>
+      </c>
       <c r="R56" t="n">
         <v>36</v>
       </c>
@@ -3821,6 +3986,9 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="Q57" t="b">
+        <v>0</v>
+      </c>
       <c r="R57" t="n">
         <v>36</v>
       </c>
@@ -3880,6 +4048,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q58" t="b">
+        <v>0</v>
+      </c>
       <c r="R58" t="n">
         <v>36</v>
       </c>
@@ -3939,6 +4110,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q59" t="b">
+        <v>0</v>
+      </c>
       <c r="R59" t="n">
         <v>36</v>
       </c>
@@ -3998,6 +4172,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q60" t="b">
+        <v>0</v>
+      </c>
       <c r="R60" t="n">
         <v>36</v>
       </c>
@@ -4057,6 +4234,9 @@
           <t>JANADIP</t>
         </is>
       </c>
+      <c r="Q61" t="b">
+        <v>0</v>
+      </c>
       <c r="R61" t="n">
         <v>36</v>
       </c>
@@ -4116,6 +4296,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q62" t="b">
+        <v>0</v>
+      </c>
       <c r="R62" t="n">
         <v>36</v>
       </c>
@@ -4175,6 +4358,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q63" t="b">
+        <v>0</v>
+      </c>
       <c r="R63" t="n">
         <v>36</v>
       </c>
@@ -4234,6 +4420,9 @@
           <t>YKP</t>
         </is>
       </c>
+      <c r="Q64" t="b">
+        <v>0</v>
+      </c>
       <c r="R64" t="n">
         <v>36</v>
       </c>
@@ -4293,6 +4482,9 @@
           <t>WAP</t>
         </is>
       </c>
+      <c r="Q65" t="b">
+        <v>0</v>
+      </c>
       <c r="R65" t="n">
         <v>36</v>
       </c>
@@ -4352,6 +4544,9 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="Q66" t="b">
+        <v>0</v>
+      </c>
       <c r="R66" t="n">
         <v>36</v>
       </c>
@@ -4411,6 +4606,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q67" t="b">
+        <v>0</v>
+      </c>
       <c r="R67" t="n">
         <v>36</v>
       </c>
@@ -4470,6 +4668,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q68" t="b">
+        <v>0</v>
+      </c>
       <c r="R68" t="n">
         <v>36</v>
       </c>
@@ -4529,6 +4730,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q69" t="b">
+        <v>0</v>
+      </c>
       <c r="R69" t="n">
         <v>36</v>
       </c>
@@ -4588,6 +4792,9 @@
           <t>JANADIP</t>
         </is>
       </c>
+      <c r="Q70" t="b">
+        <v>0</v>
+      </c>
       <c r="R70" t="n">
         <v>36</v>
       </c>
@@ -4647,6 +4854,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q71" t="b">
+        <v>0</v>
+      </c>
       <c r="R71" t="n">
         <v>36</v>
       </c>
@@ -4706,6 +4916,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q72" t="b">
+        <v>0</v>
+      </c>
       <c r="R72" t="n">
         <v>36</v>
       </c>
@@ -4765,6 +4978,9 @@
           <t>YKP</t>
         </is>
       </c>
+      <c r="Q73" t="b">
+        <v>0</v>
+      </c>
       <c r="R73" t="n">
         <v>36</v>
       </c>
@@ -4824,6 +5040,9 @@
           <t>WAP</t>
         </is>
       </c>
+      <c r="Q74" t="b">
+        <v>0</v>
+      </c>
       <c r="R74" t="n">
         <v>36</v>
       </c>
@@ -4883,6 +5102,9 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="Q75" t="b">
+        <v>0</v>
+      </c>
       <c r="R75" t="n">
         <v>36</v>
       </c>
@@ -4942,6 +5164,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q76" t="b">
+        <v>1</v>
+      </c>
       <c r="R76" t="n">
         <v>36</v>
       </c>
@@ -5001,6 +5226,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q77" t="b">
+        <v>0</v>
+      </c>
       <c r="R77" t="n">
         <v>36</v>
       </c>
@@ -5060,6 +5288,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q78" t="b">
+        <v>0</v>
+      </c>
       <c r="R78" t="n">
         <v>36</v>
       </c>
@@ -5119,6 +5350,9 @@
           <t>JANADIP</t>
         </is>
       </c>
+      <c r="Q79" t="b">
+        <v>0</v>
+      </c>
       <c r="R79" t="n">
         <v>36</v>
       </c>
@@ -5178,6 +5412,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q80" t="b">
+        <v>0</v>
+      </c>
       <c r="R80" t="n">
         <v>36</v>
       </c>
@@ -5237,6 +5474,9 @@
           <t>YKP</t>
         </is>
       </c>
+      <c r="Q81" t="b">
+        <v>0</v>
+      </c>
       <c r="R81" t="n">
         <v>36</v>
       </c>
@@ -5296,6 +5536,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q82" t="b">
+        <v>0</v>
+      </c>
       <c r="R82" t="n">
         <v>36</v>
       </c>
@@ -5355,6 +5598,9 @@
           <t>WAP</t>
         </is>
       </c>
+      <c r="Q83" t="b">
+        <v>0</v>
+      </c>
       <c r="R83" t="n">
         <v>36</v>
       </c>
@@ -5414,6 +5660,9 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="Q84" t="b">
+        <v>0</v>
+      </c>
       <c r="R84" t="n">
         <v>36</v>
       </c>
@@ -5473,6 +5722,9 @@
           <t>RJD</t>
         </is>
       </c>
+      <c r="Q85" t="b">
+        <v>0</v>
+      </c>
       <c r="R85" t="n">
         <v>36</v>
       </c>
@@ -5532,6 +5784,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q86" t="b">
+        <v>0</v>
+      </c>
       <c r="R86" t="n">
         <v>36</v>
       </c>
@@ -5591,6 +5846,9 @@
           <t>HAMS</t>
         </is>
       </c>
+      <c r="Q87" t="b">
+        <v>0</v>
+      </c>
       <c r="R87" t="n">
         <v>36</v>
       </c>
@@ -5650,6 +5908,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q88" t="b">
+        <v>0</v>
+      </c>
       <c r="R88" t="n">
         <v>36</v>
       </c>
@@ -5709,6 +5970,9 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="Q89" t="b">
+        <v>0</v>
+      </c>
       <c r="R89" t="n">
         <v>36</v>
       </c>
@@ -5768,6 +6032,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q90" t="b">
+        <v>0</v>
+      </c>
       <c r="R90" t="n">
         <v>36</v>
       </c>
@@ -5827,6 +6094,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q91" t="b">
+        <v>0</v>
+      </c>
       <c r="R91" t="n">
         <v>36</v>
       </c>
@@ -5886,6 +6156,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q92" t="b">
+        <v>0</v>
+      </c>
       <c r="R92" t="n">
         <v>36</v>
       </c>
@@ -5945,6 +6218,9 @@
           <t>RSPSR</t>
         </is>
       </c>
+      <c r="Q93" t="b">
+        <v>0</v>
+      </c>
       <c r="R93" t="n">
         <v>36</v>
       </c>
@@ -6004,6 +6280,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q94" t="b">
+        <v>0</v>
+      </c>
       <c r="R94" t="n">
         <v>36</v>
       </c>
@@ -6063,6 +6342,9 @@
           <t>VCSMP</t>
         </is>
       </c>
+      <c r="Q95" t="b">
+        <v>0</v>
+      </c>
       <c r="R95" t="n">
         <v>36</v>
       </c>
@@ -6122,6 +6404,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q96" t="b">
+        <v>0</v>
+      </c>
       <c r="R96" t="n">
         <v>36</v>
       </c>
@@ -6181,6 +6466,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q97" t="b">
+        <v>0</v>
+      </c>
       <c r="R97" t="n">
         <v>36</v>
       </c>
@@ -6240,6 +6528,9 @@
           <t>BDlP</t>
         </is>
       </c>
+      <c r="Q98" t="b">
+        <v>0</v>
+      </c>
       <c r="R98" t="n">
         <v>36</v>
       </c>
@@ -6299,6 +6590,9 @@
           <t>RJD</t>
         </is>
       </c>
+      <c r="Q99" t="b">
+        <v>0</v>
+      </c>
       <c r="R99" t="n">
         <v>36</v>
       </c>
@@ -6358,6 +6652,9 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="Q100" t="b">
+        <v>0</v>
+      </c>
       <c r="R100" t="n">
         <v>36</v>
       </c>
@@ -6417,6 +6714,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q101" t="b">
+        <v>0</v>
+      </c>
       <c r="R101" t="n">
         <v>36</v>
       </c>
@@ -6476,6 +6776,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q102" t="b">
+        <v>0</v>
+      </c>
       <c r="R102" t="n">
         <v>36</v>
       </c>
@@ -6534,6 +6837,9 @@
         <is>
           <t>IND</t>
         </is>
+      </c>
+      <c r="Q103" t="b">
+        <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>36</v>
